--- a/created_tasks.xlsx
+++ b/created_tasks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,206 +477,698 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3282</v>
+        <v>3480</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>X1 - Configurar App OKTA (OIDC SPA)</t>
+          <t>E0.1.1 - Extender AreasCache con sensitivity + id por área</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OKTA/infra</t>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>App OKTA (OIDC SPA, redirect URIs, scopes openid profile email) + datos issuer/client_id</t>
+          <t>Modificar get_polygons() o agregar get_pixel_change_areas(cam_key, w, h) en app/areas_cache.py, propagando sensitivity y un id estable (indice) por poligono, sin alterar el contrato actual usado por punto_dentro_de_area(). | Criterios de aceptacion (H1): get_polygons/nuevo metodo expone sensitivity + id por area sin romper el flujo BNBULTRA existente.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>3281</v>
+        <v>3479</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Black and Blue\Sprint 61</t>
+          <t>Black and Blue\Sprint 71</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>manuel.betancourt@blacknblue.app</t>
+          <t>samir.millan@blacknblue.app</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-24T15:08:28.823Z</t>
+          <t>2026-08-31T18:50:45.92Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3283</v>
+        <v>3481</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>X2 - Gateway APIM: exponer endpoints SSO</t>
+          <t>E0.1.2 - Fijar y documentar convención de unidades de sensitivity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gateway APIM: exponer /auth/sso/discovery y /users/auth/okta sin auth previa + CORS</t>
+          <t>Decidir 0.0-1.0 vs 0-100% en un solo punto de conversion (los datos reales de areas_cameras.json guardan floats 0.0-1.0); documentar la decision en el codigo. | Criterios de aceptacion (H1): una sola convencion de unidades usada en toda la comparacion, sin mezclar 0-1 y 0-100.</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3281</v>
+        <v>3479</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Black and Blue\Sprint 61</t>
+          <t>Black and Blue\Sprint 71</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>manuel.betancourt@blacknblue.app</t>
+          <t>samir.millan@blacknblue.app</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-24T15:08:59.947Z</t>
+          <t>2026-08-31T18:51:32.133Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3284</v>
+        <v>3482</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X3 - Seed inicial: dominios Asbury</t>
+          <t>E0.1.3 - Test: invalidación de caché de máscaras con áreas pixel_change</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Backend/DB</t>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Seed inicial: cargar dominios del cliente Asbury → site_id</t>
+          <t>Modificar areas_cameras.json con un area pixel_change y confirmar que la mascara se recalcula. | Criterios de aceptacion (H1): CA-07 verificado con test ejecutable.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3281</v>
+        <v>3479</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Black and Blue\Sprint 61</t>
+          <t>Black and Blue\Sprint 71</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>manuel.betancourt@blacknblue.app</t>
+          <t>samir.millan@blacknblue.app</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-24T15:09:26.023Z</t>
+          <t>2026-08-31T18:52:20.89Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3285</v>
+        <v>3483</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X4 - QA E2E login OKTA</t>
+          <t>E0.1.4 - Test: canales sin pixel_change no cambian de comportamiento</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QA E2E (login tradicional intacto + login OKTA por dominio)</t>
+          <t>Confirmar que un canal sin areas pixel_change no invoca ninguna ruta nueva de AreasCache. | Criterios de aceptacion (H1): RF-12 verificado, cero overhead en canales sin pixel_change.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3281</v>
+        <v>3479</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Black and Blue\Sprint 61</t>
+          <t>Black and Blue\Sprint 71</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>manuel.betancourt@blacknblue.app</t>
+          <t>samir.millan@blacknblue.app</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-24T15:09:49.433Z</t>
+          <t>2026-08-31T18:52:50.5Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3286</v>
+        <v>3484</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>X5 - Despliegue coordinado + runbook</t>
+          <t>E0.2.1 - Implementar cálculo de diff (resize + grayscale + absdiff)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Despliegue coordinado (migración → core-api → front) + runbook</t>
+          <t>En motion_websocket_listener.py: reducir el frame al 25%, convertir a escala de grises, cv2.absdiff contra _prev_frame, umbral de intensidad 25/255. | Criterios de aceptacion (H2): RF-10/RF-11 cumplidos, calculo verificado sobre frames reales.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>3281</v>
+        <v>3479</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Black and Blue\Sprint 61</t>
+          <t>Black and Blue\Sprint 71</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>manuel.betancourt@blacknblue.app</t>
+          <t>samir.millan@blacknblue.app</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-24T15:10:16.773Z</t>
+          <t>2026-08-31T18:53:24.143Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3485</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>E0.2.2 - Implementar _prev_frame por instancia, antes del gate de MIN_FRAME_INTERVAL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mover la actualizacion de _prev_frame y la evaluacion de pixel_change antes del return temprano de _handle_binary_frame, para que RF-07 se cumpla independientemente de los valores de throttle. | Criterios de aceptacion (H2): _prev_frame se actualiza con cada frame recibido, no solo los que pasan el gate de YOLO.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:55:49.353Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3486</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>E0.2.3 - Evaluación independiente por área usando máscara + sensitivity</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Aplicar la mascara de cada area pixel_change (de E0.1.1) sobre el diff, calcular porcentaje de cambio y comparar contra su sensitivity propia; soporta multiples areas por canal sin interferencia entre ellas. | Criterios de aceptacion (H2): RF-04/RF-05 cumplidos, evaluacion independiente confirmada.</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:56:26.117Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3487</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E0.2.4 - Test: CA-01, CA-02, CA-05, CA-06, CA-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Casos: umbral no superado (sin alerta), umbral superado (alerta inmediata), sensitivity=0 (cualquier cambio activa), primer frame (sin alerta, solo referencia), actualizacion de _prev_frame sin alerta cuando no se supera el umbral. | Criterios de aceptacion (H2): los cinco CA verificados con tests ejecutables.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:57:04.267Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3488</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E0.2.5 - Test: CA-04 (múltiples áreas, alertas independientes)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Dos areas con sensitivity distinto superan su umbral simultaneamente, se deben generar dos alertas independientes, una por area. | Criterios de aceptacion (H2): CA-04 verificado, activacion de un area no modifica el estado de las demas.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:58:27.137Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3489</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E0.3.1 - Construir y enviar el payload de alerta pixel_change</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Armar el mensaje (areas_key, canal, area activada, tipo pixel_change) y enviarlo via NotifyService.send_notification() directamente desde MotionWebSocketListener. | Criterios de aceptacion (H3): RF-06/RF-15 cumplidos, sin pasar por _process_snapshot ni camera_events.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:59:14.507Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3490</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E0.3.2 - Definir e implementar cooldown/debounce para pixel_change</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Decision pendiente identificada en la revision del documento: evitar alertas repetidas mientras un area se mantiene activa, sin retrasar la primera notificacion. | Criterios de aceptacion (H3): CA-02 (alerta inmediata) cumplido; estrategia de debounce documentada e implementada.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:00:01.177Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3491</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>E0.3.3 - Test: alerta inmediata + estructura de BNBULTRA intacta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Verificar CA-02 (alerta inmediata en la primera activacion) y que la estructura/persistencia de eventos BNBULTRA no cambia. | Criterios de aceptacion (H3): alerta enviada sin alterar camera_events ni el flujo BNBULTRA existente.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:01:19.217Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3492</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E0.4.1 - Cambiar default de MIN_FRAME_INTERVAL a 0.5s + medir impacto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ajustar configyolo.py y medir el efecto en la carga del _GlobalManager.yolo_semaphore antes de fijarlo como default de produccion. | Criterios de aceptacion (H4): nuevo default sin degradar el pool de inferencia YOLO.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:02:03.867Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3493</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>E0.4.2 - Investigar y documentar el ajuste de FPS de go2rtc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Determinar si 1 FPS a 2 FPS aplica a un setting fuera de este repo (go2rtc.yaml) y documentar el hallazgo; el polling de start_motion_listener() ya corre a 0.5s hoy. | Criterios de aceptacion (H4): hallazgo documentado, decision explicita de si aplica o no cambio adicional.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:04:21.183Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3494</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>E0.4.3 - Test de no regresión en canales sin pixel_change</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Confirmar que la latencia/comportamiento de canales sin areas pixel_change no cambia tras los ajustes de configuracion. | Criterios de aceptacion (H4): RNF-04 verificado, 0 ms de overhead adicional en canales sin pixel_change.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:06:04.283Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3495</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E0.5.1 - Benchmark de latencia por frame</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Medir el costo real de resize + grayscale + absdiff + mascaras en un escenario representativo, confirmar menos de 2 ms por frame por camara. | Criterios de aceptacion (H5): RNF-01/RNF-05 verificados, sin bloquear el event loop de asyncio.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:06:36.283Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3496</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E0.5.2 - Prueba de memoria sostenida (80 cámaras, 1 hora)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pixel Areas Backend (bnb-local-detection)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Simular 80 camaras con pixel_change activo durante al menos una hora y medir el consumo total de _prev_frame. | Criterios de aceptacion (H5): CA-09 verificado, consumo menor a 200 MB.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Black and Blue\Sprint 71</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>samir.millan@blacknblue.app</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:10:26.077Z</t>
         </is>
       </c>
     </row>
